--- a/backend/templates/sao_ke_tt_theo_du_an.xlsx
+++ b/backend/templates/sao_ke_tt_theo_du_an.xlsx
@@ -710,26 +710,26 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>257175</xdr:colOff>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>219075</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D73BDFEA-77F9-846B-04BC-DD2B076F2AE1}"/>
+              <a16:creationId id="{D73BDFEA-77F9-846B-04BC-DD2B076F2AE1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -738,15 +738,15 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:blip r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="257175" y="2133600"/>
-          <a:ext cx="476250" cy="476250"/>
+          <a:off x="0" y="1714500"/>
+          <a:ext cx="2743200" cy="1097280"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -773,10 +773,10 @@
         <xdr:cNvPr id="4" name="Picture 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4BED79A2-C0BF-5BD4-876D-5F228E845E0C}"/>
+              <a16:creationId id="{4BED79A2-C0BF-5BD4-876D-5F228E845E0C}"/>
             </a:ext>
             <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{D73BDFEA-77F9-846B-04BC-DD2B076F2AE1}"/>
+              <a16:predDERef pred="{D73BDFEA-77F9-846B-04BC-DD2B076F2AE1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -785,7 +785,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:blip r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1077,7 +1077,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -1156,9 +1156,7 @@
     </row>
     <row r="7" spans="1:5" ht="22.5" customHeight="1">
       <c r="A7" s="3"/>
-      <c r="B7" s="36" t="s">
-        <v>10</v>
-      </c>
+      <c r="B7" s="36"/>
       <c r="C7" s="36"/>
       <c r="D7" s="37" t="s">
         <v>11</v>

--- a/backend/templates/sao_ke_tt_theo_du_an.xlsx
+++ b/backend/templates/sao_ke_tt_theo_du_an.xlsx
@@ -803,21 +803,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{68E53EB8-FD1A-4AA9-9E81-1495ABEA4FCE}" name="Table1" displayName="Table1" ref="A8:F12" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8" headerRowBorderDxfId="6" tableBorderDxfId="7" totalsRowBorderDxfId="5">
-  <autoFilter ref="A8:F12" xr:uid="{68E53EB8-FD1A-4AA9-9E81-1495ABEA4FCE}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{4D1C5451-8DAC-4C0C-A2F5-7732B47DEA04}" name="STT" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{B79BC3B4-3AFD-4BA3-86C9-2386AFCD2550}" name="Họ tên" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{F8BDC4AC-E99E-4DE2-872F-38DA43D8AB6F}" name="CCCD" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{E4623EC1-2C6E-416E-B0FC-E1D9C4F516AA}" name="Dự án" dataDxfId="1"/>
-    <tableColumn id="6" xr3:uid="{75190708-1BC8-46D5-8C71-E3A86E561AD7}" name="Số tiền"/>
-    <tableColumn id="5" xr3:uid="{9B07B4F5-CE3F-4731-AD0B-CD60D14F13E7}" name="Ngày trả" dataDxfId="0"/>
-  </tableColumns>
-  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1466,8 +1451,5 @@
     <mergeCell ref="A4:B4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
--- a/backend/templates/sao_ke_tt_theo_du_an.xlsx
+++ b/backend/templates/sao_ke_tt_theo_du_an.xlsx
@@ -73,13 +73,13 @@
     <t>Chủ Tài Khoản</t>
   </si>
   <si>
-    <t>NGUYEN VIET DUNG</t>
+    <t>CONG TY TNHH MTV GPPM TING TING</t>
   </si>
   <si>
     <t>Số Tài Khoản</t>
   </si>
   <si>
-    <t>1357210887</t>
+    <t>283866888</t>
   </si>
   <si>
     <t>Ngân Hàng</t>

--- a/backend/templates/sao_ke_tt_theo_du_an.xlsx
+++ b/backend/templates/sao_ke_tt_theo_du_an.xlsx
@@ -1073,7 +1073,7 @@
     <col min="2" max="2" width="17.140625" style="1" customWidth="1"/>
     <col min="3" max="3" width="16" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="26" style="1" customWidth="1"/>
-    <col min="5" max="5" width="24.28515625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="38" style="2" customWidth="1"/>
     <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>

--- a/backend/templates/sao_ke_tt_theo_du_an.xlsx
+++ b/backend/templates/sao_ke_tt_theo_du_an.xlsx
@@ -2,10 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29618"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{285A0B7B-E0F0-414E-A546-8B718C6956A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookPr filterPrivacy="true"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -124,89 +123,95 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0\ &quot;₫&quot;"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="14">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
     </font>
     <font>
-      <b/>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF323232"/>
       <sz val="11"/>
-      <color rgb="FF323232"/>
-      <name val="Arial"/>
     </font>
     <font>
-      <b/>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
     </font>
     <font>
+      <name val="Arial"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
     </font>
     <font>
+      <name val="Arial"/>
+      <color rgb="FF000000"/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
     </font>
     <font>
-      <b/>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF000000"/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
     </font>
     <font>
-      <b/>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FFFF0000"/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Arial"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF323232"/>
       <name val="Arial"/>
       <charset val="1"/>
+      <b val="1"/>
+      <color rgb="FF323232"/>
+      <sz val="11"/>
     </font>
     <font>
-      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <sz val="11"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="10"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="10"/>
     </font>
     <font>
-      <b/>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF000000"/>
       <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
     </font>
     <font>
-      <sz val="10"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -226,13 +231,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <fgColor theme="0" tint="-0.1499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
+        <fgColor theme="5" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -240,6 +245,11 @@
       <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -331,113 +341,116 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="true" applyFill="true"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment indent="2" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" indent="1" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
+      <alignment horizontal="right" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyAlignment="true">
+      <alignment horizontal="left" indent="1" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="6" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="6" borderId="0" xfId="0" quotePrefix="true" applyNumberFormat="true" applyFont="true" applyFill="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" indent="1" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="true" applyFill="true"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" indent="6"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
+      <alignment horizontal="left" indent="6" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="6"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" indent="6" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
       <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="7" borderId="0" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -446,23 +459,23 @@
   <dxfs count="10">
     <dxf>
       <font>
+        <name val="Calibri"/>
+        <family val="2"/>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
         <condense val="0"/>
         <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
+        <color auto="true"/>
+        <sz val="10"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
         <scheme val="none"/>
       </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <alignment horizontal="general" vertical="center"/>
+      <border>
         <left style="thin">
           <color rgb="FFCCCCCC"/>
         </left>
@@ -481,23 +494,23 @@
     </dxf>
     <dxf>
       <font>
+        <name val="Calibri"/>
+        <family val="2"/>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
         <condense val="0"/>
         <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
+        <color auto="true"/>
+        <sz val="10"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
         <scheme val="none"/>
       </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <alignment horizontal="general" vertical="center"/>
+      <border>
         <left style="thin">
           <color rgb="FFCCCCCC"/>
         </left>
@@ -516,23 +529,23 @@
     </dxf>
     <dxf>
       <font>
+        <name val="Calibri"/>
+        <family val="2"/>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
         <condense val="0"/>
         <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
+        <color auto="true"/>
+        <sz val="10"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
         <scheme val="none"/>
       </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <alignment horizontal="general" vertical="center"/>
+      <border>
         <left style="thin">
           <color rgb="FFCCCCCC"/>
         </left>
@@ -551,23 +564,23 @@
     </dxf>
     <dxf>
       <font>
+        <name val="Calibri"/>
+        <family val="2"/>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
         <condense val="0"/>
         <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
+        <color auto="true"/>
+        <sz val="10"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
         <scheme val="none"/>
       </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <alignment horizontal="general" vertical="center"/>
+      <border>
         <left style="thin">
           <color rgb="FFCCCCCC"/>
         </left>
@@ -586,23 +599,23 @@
     </dxf>
     <dxf>
       <font>
+        <name val="Calibri"/>
+        <family val="2"/>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
         <condense val="0"/>
         <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
+        <color auto="true"/>
+        <sz val="10"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
         <scheme val="none"/>
       </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <alignment horizontal="general" vertical="center"/>
+      <border>
         <left style="thin">
           <color rgb="FFCCCCCC"/>
         </left>
@@ -620,21 +633,21 @@
       </border>
     </dxf>
     <dxf>
-      <border outline="0">
+      <border>
         <top style="thin">
           <color rgb="FFCCCCCC"/>
         </top>
       </border>
     </dxf>
     <dxf>
-      <border outline="0">
+      <border>
         <bottom style="thin">
           <color rgb="FF000000"/>
         </bottom>
       </border>
     </dxf>
     <dxf>
-      <border outline="0">
+      <border>
         <top style="thin">
           <color rgb="FF000000"/>
         </top>
@@ -645,47 +658,47 @@
     </dxf>
     <dxf>
       <font>
+        <name val="Calibri"/>
+        <family val="2"/>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
         <condense val="0"/>
         <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
+        <color auto="true"/>
+        <sz val="10"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
         <scheme val="none"/>
       </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="general" vertical="center"/>
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <name val="Arial"/>
+        <b val="1"/>
         <i val="0"/>
         <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
         <condense val="0"/>
         <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
+        <color rgb="FF000000"/>
+        <sz val="10"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
         <scheme val="none"/>
       </font>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
-          <bgColor theme="0" tint="-0.14999847407452621"/>
+          <bgColor theme="0" tint="-0.1499984740745262"/>
         </patternFill>
       </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <alignment horizontal="center" indent="1" vertical="center"/>
+      <border>
         <left style="thin">
           <color rgb="FF000000"/>
         </left>
@@ -697,7 +710,7 @@
       </border>
     </dxf>
   </dxfs>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -806,7 +819,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1064,20 +1077,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:E64"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="true"/>
   <cols>
-    <col min="1" max="1" width="7.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="17.140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="16" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26" style="1" customWidth="1"/>
-    <col min="5" max="5" width="38" style="2" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col customWidth="true" max="1" min="1" style="1" width="7.7109375"/>
+    <col customWidth="true" max="2" min="2" style="1" width="17.140625"/>
+    <col bestFit="true" customWidth="true" max="3" min="3" style="2" width="16"/>
+    <col customWidth="true" max="4" min="4" style="1" width="26"/>
+    <col customWidth="true" max="5" min="5" style="2" width="24.28515625"/>
+    <col max="16384" min="6" style="1" width="9.140625"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="22.5" customHeight="1">
+    <row r="1" spans="1:5" ht="22.5" customHeight="true">
       <c r="A1" s="28"/>
       <c r="B1" s="38" t="s">
         <v>0</v>
@@ -1088,7 +1101,7 @@
       </c>
       <c r="E1" s="37"/>
     </row>
-    <row r="2" spans="1:5" ht="22.5" customHeight="1">
+    <row r="2" spans="1:5" ht="22.5" customHeight="true">
       <c r="A2" s="6"/>
       <c r="B2" s="38"/>
       <c r="C2" s="38"/>
@@ -1099,7 +1112,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="22.5" customHeight="1">
+    <row r="3" spans="1:5" ht="22.5" customHeight="true">
       <c r="A3" s="6"/>
       <c r="B3" s="38"/>
       <c r="C3" s="38"/>
@@ -1110,7 +1123,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="22.5" customHeight="1">
+    <row r="4" spans="1:5" ht="22.5" customHeight="true">
       <c r="A4" s="30"/>
       <c r="B4" s="38"/>
       <c r="C4" s="38"/>
@@ -1121,7 +1134,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="22.5" customHeight="1">
+    <row r="5" spans="1:5" ht="22.5" customHeight="true">
       <c r="A5" s="29"/>
       <c r="B5" s="38"/>
       <c r="C5" s="38"/>
@@ -1132,14 +1145,14 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="22.5" customHeight="1">
+    <row r="6" spans="1:5" ht="22.5" customHeight="true">
       <c r="A6" s="3"/>
       <c r="B6" s="3"/>
       <c r="C6" s="4"/>
       <c r="D6" s="11"/>
       <c r="E6" s="12"/>
     </row>
-    <row r="7" spans="1:5" ht="22.5" customHeight="1">
+    <row r="7" spans="1:5" ht="22.5" customHeight="true">
       <c r="A7" s="3"/>
       <c r="B7" s="36"/>
       <c r="C7" s="36"/>
@@ -1148,18 +1161,18 @@
       </c>
       <c r="E7" s="37"/>
     </row>
-    <row r="8" spans="1:5" ht="22.5" customHeight="1">
+    <row r="8" spans="1:5" ht="32" customHeight="true">
       <c r="A8" s="5"/>
       <c r="B8" s="36"/>
       <c r="C8" s="36"/>
       <c r="D8" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E8" s="18" t="s">
+      <c r="E8" s="41" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="22.5" customHeight="1">
+    <row r="9" spans="1:5" ht="22.5" customHeight="true">
       <c r="A9" s="5"/>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
@@ -1170,7 +1183,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="22.5" customHeight="1">
+    <row r="10" spans="1:5" ht="22.5" customHeight="true">
       <c r="A10" s="5"/>
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
@@ -1181,14 +1194,14 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="22.5" customHeight="1">
+    <row r="11" spans="1:5" ht="22.5" customHeight="true">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="C11" s="4"/>
       <c r="D11" s="3"/>
       <c r="E11" s="4"/>
     </row>
-    <row r="12" spans="1:5" ht="22.5" customHeight="1">
+    <row r="12" spans="1:5" ht="22.5" customHeight="true">
       <c r="A12" s="33" t="s">
         <v>18</v>
       </c>
@@ -1291,7 +1304,7 @@
     <mergeCell ref="B1:C5"/>
   </mergeCells>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
-  <pageSetup paperSize="9" fitToHeight="0" orientation="portrait"/>
+  <pageSetup fitToHeight="0" orientation="portrait" paperSize="9"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>

--- a/backend/templates/sao_ke_tt_theo_du_an.xlsx
+++ b/backend/templates/sao_ke_tt_theo_du_an.xlsx
@@ -1075,7 +1075,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>

--- a/backend/templates/sao_ke_tt_theo_du_an.xlsx
+++ b/backend/templates/sao_ke_tt_theo_du_an.xlsx
@@ -78,13 +78,13 @@
     <t>Số Tài Khoản</t>
   </si>
   <si>
-    <t>283866888</t>
+    <t>271866699</t>
   </si>
   <si>
     <t>Ngân Hàng</t>
   </si>
   <si>
-    <t>TECHCOMBANK</t>
+    <t>Ngân hàng Quân đội (MB)</t>
   </si>
   <si>
     <t>CHI TIẾT GIAO DỊCH</t>

--- a/backend/templates/sao_ke_tt_theo_du_an.xlsx
+++ b/backend/templates/sao_ke_tt_theo_du_an.xlsx
@@ -1,129 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29618"/>
-  <workbookPr filterPrivacy="true"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010" tabRatio="600" firstSheet="1" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" r:id="rId1"/>
-    <sheet name="Sample Project" sheetId="2" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sample Project" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191028"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191028" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="29">
-  <si>
-    <t>CÔNG TY CỔ PHẦN QUỐC TẾ THƯƠNG MẠI VÀ DỊCH VỤ VIỆT PHÁP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TÓM TẮT SAO KÊ </t>
-  </si>
-  <si>
-    <t>Tổng Tiền Giải Ngân</t>
-  </si>
-  <si>
-    <t>79.642.000</t>
-  </si>
-  <si>
-    <t>Phí Dịch Vụ (2%)</t>
-  </si>
-  <si>
-    <t>1.592.840</t>
-  </si>
-  <si>
-    <t>Tiền CTy Phải Trả</t>
-  </si>
-  <si>
-    <t>81.234.840</t>
-  </si>
-  <si>
-    <t>Hạn Thanh Toán</t>
-  </si>
-  <si>
-    <t>16/12/2025</t>
-  </si>
-  <si>
-    <t>HỆ THỐNG ỨNG LƯƠNG PAYROLL SYSTEM</t>
-  </si>
-  <si>
-    <t>TÀI KHOẢN THỤ HƯỞNG</t>
-  </si>
-  <si>
-    <t>Chủ Tài Khoản</t>
-  </si>
-  <si>
-    <t>CONG TY TNHH MTV GPPM TING TING</t>
-  </si>
-  <si>
-    <t>Số Tài Khoản</t>
-  </si>
-  <si>
-    <t>271866699</t>
-  </si>
-  <si>
-    <t>Ngân Hàng</t>
-  </si>
-  <si>
-    <t>Ngân hàng Quân đội (MB)</t>
-  </si>
-  <si>
-    <t>CHI TIẾT GIAO DỊCH</t>
-  </si>
-  <si>
-    <t>STT</t>
-  </si>
-  <si>
-    <t>Kỳ lương tháng</t>
-  </si>
-  <si>
-    <t>Dự án</t>
-  </si>
-  <si>
-    <t>Số tiền</t>
-  </si>
-  <si>
-    <t>Tên dự án</t>
-  </si>
-  <si>
-    <t>Tổng nhân viên</t>
-  </si>
-  <si>
-    <t>Tổng tiền ứng</t>
-  </si>
-  <si>
-    <t>Họ tên</t>
-  </si>
-  <si>
-    <t>CCCD</t>
-  </si>
-  <si>
-    <t>Ngày trả</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0\ &quot;₫&quot;"/>
   </numFmts>
@@ -213,7 +105,7 @@
   </fonts>
   <fills count="8">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -253,7 +145,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -337,121 +229,132 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="true"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+  <cellXfs count="44">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="true" applyFill="true"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment indent="2" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" indent="1" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
-      <alignment horizontal="right" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyAlignment="true">
-      <alignment horizontal="left" indent="1" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="14" fontId="4" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyAlignment="true">
+    <xf numFmtId="164" fontId="3" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyAlignment="true">
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyAlignment="true">
+    <xf numFmtId="14" fontId="4" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="6" borderId="0" xfId="0" quotePrefix="true" applyNumberFormat="true" applyFont="true" applyFill="true" applyAlignment="true">
+    <xf numFmtId="14" fontId="4" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" indent="1" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="true" applyFill="true"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
-      <alignment horizontal="left" indent="6" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1" indent="6"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left" indent="6" vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="6"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="14" fontId="13" fillId="7" borderId="0" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
+    <xf numFmtId="14" fontId="13" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -461,18 +364,14 @@
       <font>
         <name val="Calibri"/>
         <family val="2"/>
-        <b val="0"/>
-        <i val="0"/>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <condense val="0"/>
+        <color auto="1"/>
         <extend val="0"/>
-        <color auto="true"/>
         <sz val="10"/>
-        <u val="none"/>
         <vertAlign val="baseline"/>
-        <scheme val="none"/>
       </font>
       <alignment horizontal="general" vertical="center"/>
       <border>
@@ -496,18 +395,14 @@
       <font>
         <name val="Calibri"/>
         <family val="2"/>
-        <b val="0"/>
-        <i val="0"/>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <condense val="0"/>
+        <color auto="1"/>
         <extend val="0"/>
-        <color auto="true"/>
         <sz val="10"/>
-        <u val="none"/>
         <vertAlign val="baseline"/>
-        <scheme val="none"/>
       </font>
       <alignment horizontal="general" vertical="center"/>
       <border>
@@ -531,18 +426,14 @@
       <font>
         <name val="Calibri"/>
         <family val="2"/>
-        <b val="0"/>
-        <i val="0"/>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <condense val="0"/>
+        <color auto="1"/>
         <extend val="0"/>
-        <color auto="true"/>
         <sz val="10"/>
-        <u val="none"/>
         <vertAlign val="baseline"/>
-        <scheme val="none"/>
       </font>
       <alignment horizontal="general" vertical="center"/>
       <border>
@@ -566,18 +457,14 @@
       <font>
         <name val="Calibri"/>
         <family val="2"/>
-        <b val="0"/>
-        <i val="0"/>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <condense val="0"/>
+        <color auto="1"/>
         <extend val="0"/>
-        <color auto="true"/>
         <sz val="10"/>
-        <u val="none"/>
         <vertAlign val="baseline"/>
-        <scheme val="none"/>
       </font>
       <alignment horizontal="general" vertical="center"/>
       <border>
@@ -601,18 +488,14 @@
       <font>
         <name val="Calibri"/>
         <family val="2"/>
-        <b val="0"/>
-        <i val="0"/>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <condense val="0"/>
+        <color auto="1"/>
         <extend val="0"/>
-        <color auto="true"/>
         <sz val="10"/>
-        <u val="none"/>
         <vertAlign val="baseline"/>
-        <scheme val="none"/>
       </font>
       <alignment horizontal="general" vertical="center"/>
       <border>
@@ -660,18 +543,14 @@
       <font>
         <name val="Calibri"/>
         <family val="2"/>
-        <b val="0"/>
-        <i val="0"/>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <condense val="0"/>
+        <color auto="1"/>
         <extend val="0"/>
-        <color auto="true"/>
         <sz val="10"/>
-        <u val="none"/>
         <vertAlign val="baseline"/>
-        <scheme val="none"/>
       </font>
       <alignment horizontal="general" vertical="center"/>
     </dxf>
@@ -679,17 +558,14 @@
       <font>
         <name val="Arial"/>
         <b val="1"/>
-        <i val="0"/>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <condense val="0"/>
+        <color rgb="FF000000"/>
         <extend val="0"/>
-        <color rgb="FF000000"/>
         <sz val="10"/>
-        <u val="none"/>
         <vertAlign val="baseline"/>
-        <scheme val="none"/>
       </font>
       <fill>
         <patternFill patternType="solid">
@@ -697,7 +573,7 @@
           <bgColor theme="0" tint="-0.1499984740745262"/>
         </patternFill>
       </fill>
-      <alignment horizontal="center" indent="1" vertical="center"/>
+      <alignment horizontal="center" vertical="center" indent="1"/>
       <border>
         <left style="thin">
           <color rgb="FF000000"/>
@@ -710,112 +586,163 @@
       </border>
     </dxf>
   </dxfs>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId id="{D73BDFEA-77F9-846B-04BC-DD2B076F2AE1}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>10</row>
+      <rowOff>0</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Picture 1"/>
+        <cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
+      </blipFill>
+      <spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="0" y="1714500"/>
           <a:ext cx="2743200" cy="1097280"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <avLst/>
         </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>295275</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>323850</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>85725</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId id="{4BED79A2-C0BF-5BD4-876D-5F228E845E0C}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef pred="{D73BDFEA-77F9-846B-04BC-DD2B076F2AE1}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId2"/>
-        <a:stretch>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>0</col>
+      <colOff>295275</colOff>
+      <row>1</row>
+      <rowOff>114300</rowOff>
+    </from>
+    <to>
+      <col>1</col>
+      <colOff>323850</colOff>
+      <row>3</row>
+      <rowOff>85725</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Picture 3"/>
+        <cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
+      </blipFill>
+      <spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="295275" y="400050"/>
           <a:ext cx="542925" cy="542925"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <avLst/>
         </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1075,393 +1002,439 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <pageSetUpPr fitToPage="true"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E64"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="true"/>
+  <dimension ref="A1:F17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="true" max="1" min="1" style="1" width="7.7109375"/>
-    <col customWidth="true" max="2" min="2" style="1" width="17.140625"/>
-    <col bestFit="true" customWidth="true" max="3" min="3" style="2" width="16"/>
-    <col customWidth="true" max="4" min="4" style="1" width="26"/>
-    <col customWidth="true" max="5" min="5" style="2" width="24.28515625"/>
-    <col max="16384" min="6" style="1" width="9.140625"/>
+    <col width="7.7109375" customWidth="1" style="28" min="1" max="1"/>
+    <col width="17.140625" customWidth="1" style="28" min="2" max="2"/>
+    <col width="16" bestFit="1" customWidth="1" style="2" min="3" max="3"/>
+    <col width="26" customWidth="1" style="28" min="4" max="4"/>
+    <col width="24.28515625" customWidth="1" style="2" min="5" max="5"/>
+    <col width="9.140625" customWidth="1" style="28" min="6" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="22.5" customHeight="true">
-      <c r="A1" s="28"/>
-      <c r="B1" s="38" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="38"/>
-      <c r="D1" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="37"/>
-    </row>
-    <row r="2" spans="1:5" ht="22.5" customHeight="true">
-      <c r="A2" s="6"/>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="E2" s="15" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="22.5" customHeight="true">
-      <c r="A3" s="6"/>
-      <c r="B3" s="38"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="22.5" customHeight="true">
-      <c r="A4" s="30"/>
-      <c r="B4" s="38"/>
-      <c r="C4" s="38"/>
-      <c r="D4" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="E4" s="16" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="22.5" customHeight="true">
-      <c r="A5" s="29"/>
-      <c r="B5" s="38"/>
-      <c r="C5" s="38"/>
-      <c r="D5" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="17" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="22.5" customHeight="true">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="12"/>
-    </row>
-    <row r="7" spans="1:5" ht="22.5" customHeight="true">
-      <c r="A7" s="3"/>
-      <c r="B7" s="36"/>
-      <c r="C7" s="36"/>
-      <c r="D7" s="37" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="37"/>
-    </row>
-    <row r="8" spans="1:5" ht="32" customHeight="true">
-      <c r="A8" s="5"/>
-      <c r="B8" s="36"/>
-      <c r="C8" s="36"/>
-      <c r="D8" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" s="41" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="22.5" customHeight="true">
-      <c r="A9" s="5"/>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E9" s="19" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="22.5" customHeight="true">
-      <c r="A10" s="5"/>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E10" s="20" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="22.5" customHeight="true">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="4"/>
-    </row>
-    <row r="12" spans="1:5" ht="22.5" customHeight="true">
-      <c r="A12" s="33" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" s="33"/>
-      <c r="C12" s="33"/>
-      <c r="D12" s="33"/>
-      <c r="E12" s="33"/>
-    </row>
-    <row r="13" spans="1:5" ht="14.25"/>
-    <row r="14" spans="1:5">
-      <c r="A14" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B14" s="34" t="s">
-        <v>20</v>
-      </c>
-      <c r="C14" s="35"/>
-      <c r="D14" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="14.25">
-      <c r="A15" s="24"/>
-      <c r="B15" s="24"/>
-      <c r="C15" s="24"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="24"/>
-    </row>
-    <row r="16" spans="1:5" ht="14.25">
-      <c r="A16" s="25"/>
-      <c r="B16" s="25"/>
-      <c r="C16" s="25"/>
-      <c r="D16" s="25"/>
-      <c r="E16" s="25"/>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-    </row>
-    <row r="18" spans="1:5" ht="14.25"/>
-    <row r="19" spans="1:5" ht="14.25"/>
-    <row r="20" spans="1:5" ht="14.25"/>
-    <row r="21" spans="1:5" ht="14.25"/>
-    <row r="22" spans="1:5" ht="14.25"/>
-    <row r="23" spans="1:5" ht="14.25"/>
-    <row r="24" spans="1:5" ht="14.25"/>
-    <row r="25" spans="1:5" ht="14.25"/>
-    <row r="26" spans="1:5" ht="14.25"/>
-    <row r="27" spans="1:5" ht="14.25"/>
-    <row r="28" spans="1:5" ht="14.25"/>
-    <row r="29" spans="1:5" ht="14.25"/>
-    <row r="30" spans="1:5" ht="14.25"/>
-    <row r="31" spans="1:5" ht="14.25"/>
-    <row r="32" spans="1:5" ht="14.25"/>
-    <row r="33" ht="14.25"/>
-    <row r="34" ht="14.25"/>
-    <row r="35" ht="14.25"/>
-    <row r="36" ht="14.25"/>
-    <row r="37" ht="14.25"/>
-    <row r="38" ht="14.25"/>
-    <row r="39" ht="14.25"/>
-    <row r="40" ht="14.25"/>
-    <row r="41" ht="14.25"/>
-    <row r="42" ht="14.25"/>
-    <row r="43" ht="14.25"/>
-    <row r="44" ht="14.25"/>
-    <row r="45" ht="14.25"/>
-    <row r="46" ht="14.25"/>
-    <row r="47" ht="14.25"/>
-    <row r="48" ht="14.25"/>
-    <row r="49" ht="14.25"/>
-    <row r="50" ht="14.25"/>
-    <row r="51" ht="14.25"/>
-    <row r="52" ht="14.25"/>
-    <row r="53" ht="14.25"/>
-    <row r="54" ht="14.25"/>
-    <row r="55" ht="14.25"/>
-    <row r="56" ht="14.25"/>
-    <row r="57" ht="14.25"/>
-    <row r="58" ht="14.25"/>
-    <row r="59" ht="14.25"/>
-    <row r="60" ht="14.25"/>
-    <row r="61" ht="14.25"/>
-    <row r="62" ht="14.25"/>
-    <row r="63" ht="14.25"/>
-    <row r="64" ht="14.25"/>
+    <row r="1" ht="22.5" customHeight="1">
+      <c r="A1" s="28" t="n"/>
+      <c r="B1" s="38" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN QUỐC TẾ THƯƠNG MẠI VÀ DỊCH VỤ VIỆT PHÁP</t>
+        </is>
+      </c>
+      <c r="D1" s="37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TÓM TẮT SAO KÊ </t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22.5" customHeight="1">
+      <c r="A2" s="6" t="n"/>
+      <c r="D2" s="9" t="inlineStr">
+        <is>
+          <t>Tổng Tiền Giải Ngân</t>
+        </is>
+      </c>
+      <c r="E2" s="15" t="inlineStr">
+        <is>
+          <t>79.642.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22.5" customHeight="1">
+      <c r="A3" s="6" t="n"/>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Phí Dịch Vụ (2%)</t>
+        </is>
+      </c>
+      <c r="E3" s="15" t="inlineStr">
+        <is>
+          <t>1.592.840</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22.5" customHeight="1">
+      <c r="A4" s="30" t="n"/>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>Tiền CTy Phải Trả</t>
+        </is>
+      </c>
+      <c r="E4" s="16" t="inlineStr">
+        <is>
+          <t>81.234.840</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22.5" customHeight="1">
+      <c r="A5" s="29" t="n"/>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>Hạn Thanh Toán</t>
+        </is>
+      </c>
+      <c r="E5" s="17" t="inlineStr">
+        <is>
+          <t>16/12/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22.5" customHeight="1">
+      <c r="A6" s="29" t="n"/>
+      <c r="B6" s="29" t="n"/>
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="11" t="n"/>
+      <c r="E6" s="12" t="n"/>
+    </row>
+    <row r="7" ht="22.5" customHeight="1">
+      <c r="A7" s="29" t="n"/>
+      <c r="B7" s="36" t="n"/>
+      <c r="D7" s="37" t="inlineStr">
+        <is>
+          <t>TÀI KHOẢN THỤ HƯỞNG</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="5" t="n"/>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>Chủ Tài Khoản</t>
+        </is>
+      </c>
+      <c r="E8" s="41" t="inlineStr">
+        <is>
+          <t>CONG TY TNHH MTV GPPM TING TING</t>
+        </is>
+      </c>
+      <c r="F8" s="42" t="n"/>
+    </row>
+    <row r="9" ht="22.5" customHeight="1">
+      <c r="A9" s="5" t="n"/>
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>Số Tài Khoản</t>
+        </is>
+      </c>
+      <c r="E9" s="19" t="inlineStr">
+        <is>
+          <t>271866699</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22.5" customHeight="1">
+      <c r="A10" s="5" t="n"/>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>Ngân Hàng</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>Ngân hàng Quân đội (MB)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22.5" customHeight="1">
+      <c r="A11" s="29" t="n"/>
+      <c r="B11" s="29" t="n"/>
+      <c r="C11" s="4" t="n"/>
+      <c r="D11" s="29" t="n"/>
+      <c r="E11" s="4" t="n"/>
+    </row>
+    <row r="12" ht="22.5" customHeight="1">
+      <c r="A12" s="33" t="inlineStr">
+        <is>
+          <t>CHI TIẾT GIAO DỊCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="14.25" customHeight="1"/>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>STT</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Kỳ lương tháng</t>
+        </is>
+      </c>
+      <c r="C14" s="43" t="n"/>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>Dự án</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>Số tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="14.25" customHeight="1">
+      <c r="A15" s="24" t="n"/>
+      <c r="B15" s="24" t="n"/>
+      <c r="C15" s="24" t="n"/>
+      <c r="D15" s="24" t="n"/>
+      <c r="E15" s="24" t="n"/>
+    </row>
+    <row r="16" ht="14.25" customHeight="1">
+      <c r="A16" s="25" t="n"/>
+      <c r="B16" s="25" t="n"/>
+      <c r="C16" s="25" t="n"/>
+      <c r="D16" s="25" t="n"/>
+      <c r="E16" s="25" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="n"/>
+      <c r="B17" s="14" t="n"/>
+      <c r="C17" s="14" t="n"/>
+      <c r="D17" s="13" t="n"/>
+      <c r="E17" s="13" t="n"/>
+    </row>
+    <row r="18" ht="14.25" customHeight="1"/>
+    <row r="19" ht="14.25" customHeight="1"/>
+    <row r="20" ht="14.25" customHeight="1"/>
+    <row r="21" ht="14.25" customHeight="1"/>
+    <row r="22" ht="14.25" customHeight="1"/>
+    <row r="23" ht="14.25" customHeight="1"/>
+    <row r="24" ht="14.25" customHeight="1"/>
+    <row r="25" ht="14.25" customHeight="1"/>
+    <row r="26" ht="14.25" customHeight="1"/>
+    <row r="27" ht="14.25" customHeight="1"/>
+    <row r="28" ht="14.25" customHeight="1"/>
+    <row r="29" ht="14.25" customHeight="1"/>
+    <row r="30" ht="14.25" customHeight="1"/>
+    <row r="31" ht="14.25" customHeight="1"/>
+    <row r="32" ht="14.25" customHeight="1"/>
+    <row r="33" ht="14.25" customHeight="1"/>
+    <row r="34" ht="14.25" customHeight="1"/>
+    <row r="35" ht="14.25" customHeight="1"/>
+    <row r="36" ht="14.25" customHeight="1"/>
+    <row r="37" ht="14.25" customHeight="1"/>
+    <row r="38" ht="14.25" customHeight="1"/>
+    <row r="39" ht="14.25" customHeight="1"/>
+    <row r="40" ht="14.25" customHeight="1"/>
+    <row r="41" ht="14.25" customHeight="1"/>
+    <row r="42" ht="14.25" customHeight="1"/>
+    <row r="43" ht="14.25" customHeight="1"/>
+    <row r="44" ht="14.25" customHeight="1"/>
+    <row r="45" ht="14.25" customHeight="1"/>
+    <row r="46" ht="14.25" customHeight="1"/>
+    <row r="47" ht="14.25" customHeight="1"/>
+    <row r="48" ht="14.25" customHeight="1"/>
+    <row r="49" ht="14.25" customHeight="1"/>
+    <row r="50" ht="14.25" customHeight="1"/>
+    <row r="51" ht="14.25" customHeight="1"/>
+    <row r="52" ht="14.25" customHeight="1"/>
+    <row r="53" ht="14.25" customHeight="1"/>
+    <row r="54" ht="14.25" customHeight="1"/>
+    <row r="55" ht="14.25" customHeight="1"/>
+    <row r="56" ht="14.25" customHeight="1"/>
+    <row r="57" ht="14.25" customHeight="1"/>
+    <row r="58" ht="14.25" customHeight="1"/>
+    <row r="59" ht="14.25" customHeight="1"/>
+    <row r="60" ht="14.25" customHeight="1"/>
+    <row r="61" ht="14.25" customHeight="1"/>
+    <row r="62" ht="14.25" customHeight="1"/>
+    <row r="63" ht="14.25" customHeight="1"/>
+    <row r="64" ht="14.25" customHeight="1"/>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="A12:E12"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B7:C8"/>
     <mergeCell ref="D7:E7"/>
     <mergeCell ref="D1:E1"/>
+    <mergeCell ref="B7:C8"/>
+    <mergeCell ref="B14:C14"/>
     <mergeCell ref="B1:C5"/>
+    <mergeCell ref="E8:F8"/>
   </mergeCells>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
-  <pageSetup fitToHeight="0" orientation="portrait" paperSize="9"/>
-  <drawing r:id="rId1"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8435EE2-9C17-433B-9C5D-06AC9500BBAE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.28515625" customWidth="1"/>
-    <col min="3" max="3" width="14.7109375" customWidth="1"/>
-    <col min="4" max="5" width="24.140625" customWidth="1"/>
-    <col min="6" max="6" width="15.140625" customWidth="1"/>
+    <col width="7.140625" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="23.28515625" customWidth="1" min="2" max="2"/>
+    <col width="14.7109375" customWidth="1" min="3" max="3"/>
+    <col width="24.140625" customWidth="1" min="4" max="5"/>
+    <col width="15.140625" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="40" t="s">
-        <v>23</v>
-      </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="40" t="s">
-        <v>24</v>
-      </c>
-      <c r="B2" s="40"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="40" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" s="40"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="27"/>
-      <c r="E3" s="27"/>
-      <c r="F3" s="27"/>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="40" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4" s="40"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="27"/>
-      <c r="E4" s="27"/>
-      <c r="F4" s="27"/>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="27"/>
-      <c r="B5" s="27"/>
-      <c r="C5" s="27"/>
-      <c r="D5" s="27"/>
-      <c r="E5" s="27"/>
-      <c r="F5" s="27"/>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="27"/>
-      <c r="B6" s="27"/>
-      <c r="C6" s="27"/>
-      <c r="D6" s="27"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="27"/>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="39" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="39"/>
-      <c r="C7" s="39"/>
-      <c r="D7" s="39"/>
-      <c r="E7" s="39"/>
-      <c r="F7" s="39"/>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="D8" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="E8" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="F8" s="23" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="24"/>
-      <c r="B9" s="24"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="31"/>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="25"/>
-      <c r="B10" s="25"/>
-      <c r="C10" s="25"/>
-      <c r="D10" s="25"/>
-      <c r="E10" s="25"/>
-      <c r="F10" s="25"/>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="24"/>
-      <c r="B11" s="24"/>
-      <c r="C11" s="24"/>
-      <c r="D11" s="24"/>
-      <c r="E11" s="24"/>
-      <c r="F11" s="24"/>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="25"/>
-      <c r="B12" s="25"/>
-      <c r="C12" s="32"/>
-      <c r="D12" s="32"/>
-      <c r="E12" s="32"/>
-      <c r="F12" s="32"/>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="21"/>
-      <c r="B13" s="21"/>
-      <c r="C13" s="21"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="21"/>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="21"/>
-      <c r="B14" s="21"/>
-      <c r="C14" s="21"/>
-      <c r="D14" s="21"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="21"/>
+    <row r="1">
+      <c r="A1" s="40" t="inlineStr">
+        <is>
+          <t>Tên dự án</t>
+        </is>
+      </c>
+      <c r="C1" s="26" t="n"/>
+      <c r="D1" s="27" t="n"/>
+      <c r="E1" s="27" t="n"/>
+      <c r="F1" s="27" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="40" t="inlineStr">
+        <is>
+          <t>Tổng nhân viên</t>
+        </is>
+      </c>
+      <c r="C2" s="26" t="n"/>
+      <c r="D2" s="27" t="n"/>
+      <c r="E2" s="27" t="n"/>
+      <c r="F2" s="27" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="40" t="inlineStr">
+        <is>
+          <t>Kỳ lương tháng</t>
+        </is>
+      </c>
+      <c r="C3" s="26" t="n"/>
+      <c r="D3" s="27" t="n"/>
+      <c r="E3" s="27" t="n"/>
+      <c r="F3" s="27" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="40" t="inlineStr">
+        <is>
+          <t>Tổng tiền ứng</t>
+        </is>
+      </c>
+      <c r="C4" s="26" t="n"/>
+      <c r="D4" s="27" t="n"/>
+      <c r="E4" s="27" t="n"/>
+      <c r="F4" s="27" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="27" t="n"/>
+      <c r="B5" s="27" t="n"/>
+      <c r="C5" s="27" t="n"/>
+      <c r="D5" s="27" t="n"/>
+      <c r="E5" s="27" t="n"/>
+      <c r="F5" s="27" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="27" t="n"/>
+      <c r="B6" s="27" t="n"/>
+      <c r="C6" s="27" t="n"/>
+      <c r="D6" s="27" t="n"/>
+      <c r="E6" s="27" t="n"/>
+      <c r="F6" s="27" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="39" t="inlineStr">
+        <is>
+          <t>CHI TIẾT GIAO DỊCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="22" t="inlineStr">
+        <is>
+          <t>STT</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>Họ tên</t>
+        </is>
+      </c>
+      <c r="C8" s="23" t="inlineStr">
+        <is>
+          <t>CCCD</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="inlineStr">
+        <is>
+          <t>Dự án</t>
+        </is>
+      </c>
+      <c r="E8" s="23" t="inlineStr">
+        <is>
+          <t>Số tiền</t>
+        </is>
+      </c>
+      <c r="F8" s="23" t="inlineStr">
+        <is>
+          <t>Ngày trả</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="24" t="n"/>
+      <c r="B9" s="24" t="n"/>
+      <c r="C9" s="31" t="n"/>
+      <c r="D9" s="31" t="n"/>
+      <c r="E9" s="31" t="n"/>
+      <c r="F9" s="31" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="25" t="n"/>
+      <c r="B10" s="25" t="n"/>
+      <c r="C10" s="25" t="n"/>
+      <c r="D10" s="25" t="n"/>
+      <c r="E10" s="25" t="n"/>
+      <c r="F10" s="25" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="24" t="n"/>
+      <c r="B11" s="24" t="n"/>
+      <c r="C11" s="24" t="n"/>
+      <c r="D11" s="24" t="n"/>
+      <c r="E11" s="24" t="n"/>
+      <c r="F11" s="24" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="25" t="n"/>
+      <c r="B12" s="25" t="n"/>
+      <c r="C12" s="32" t="n"/>
+      <c r="D12" s="32" t="n"/>
+      <c r="E12" s="32" t="n"/>
+      <c r="F12" s="32" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="21" t="n"/>
+      <c r="B13" s="21" t="n"/>
+      <c r="C13" s="21" t="n"/>
+      <c r="D13" s="21" t="n"/>
+      <c r="E13" s="21" t="n"/>
+      <c r="F13" s="21" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="21" t="n"/>
+      <c r="B14" s="21" t="n"/>
+      <c r="C14" s="21" t="n"/>
+      <c r="D14" s="21" t="n"/>
+      <c r="E14" s="21" t="n"/>
+      <c r="F14" s="21" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A3:B3"/>
     <mergeCell ref="A7:F7"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A4:B4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/backend/templates/sao_ke_tt_theo_du_an.xlsx
+++ b/backend/templates/sao_ke_tt_theo_du_an.xlsx
@@ -1014,7 +1014,7 @@
     <col width="17.140625" customWidth="1" style="28" min="2" max="2"/>
     <col width="16" bestFit="1" customWidth="1" style="2" min="3" max="3"/>
     <col width="26" customWidth="1" style="28" min="4" max="4"/>
-    <col width="24.28515625" customWidth="1" style="2" min="5" max="5"/>
+    <col width="38" customWidth="1" style="2" min="5" max="5"/>
     <col width="9.140625" customWidth="1" style="28" min="6" max="16384"/>
   </cols>
   <sheetData>
@@ -1111,7 +1111,6 @@
           <t>CONG TY TNHH MTV GPPM TING TING</t>
         </is>
       </c>
-      <c r="F8" s="42" t="n"/>
     </row>
     <row r="9" ht="22.5" customHeight="1">
       <c r="A9" s="5" t="n"/>
